--- a/data/nzd0487/nzd0487.xlsx
+++ b/data/nzd0487/nzd0487.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E480"/>
+  <dimension ref="A1:E482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10514,6 +10514,48 @@
       <c r="E480" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>330.71</v>
+      </c>
+      <c r="C481" t="n">
+        <v>332.59</v>
+      </c>
+      <c r="D481" t="n">
+        <v>336.89</v>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>330.47</v>
+      </c>
+      <c r="C482" t="n">
+        <v>332.2</v>
+      </c>
+      <c r="D482" t="n">
+        <v>336.84</v>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10528,7 +10570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B642"/>
+  <dimension ref="A1:B644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16951,6 +16993,26 @@
       </c>
       <c r="B642" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -17119,28 +17181,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07750520266270824</v>
+        <v>-0.07254444493684566</v>
       </c>
       <c r="J2" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K2" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009458016817817216</v>
+        <v>0.00833212982100362</v>
       </c>
       <c r="M2" t="n">
-        <v>4.463184673712485</v>
+        <v>4.464286177124981</v>
       </c>
       <c r="N2" t="n">
-        <v>29.84412796078757</v>
+        <v>29.85211286708101</v>
       </c>
       <c r="O2" t="n">
-        <v>5.462977938888969</v>
+        <v>5.463708709940621</v>
       </c>
       <c r="P2" t="n">
-        <v>326.9595231101049</v>
+        <v>326.9023492878503</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17197,28 +17259,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07425362114548695</v>
+        <v>-0.07338523057071536</v>
       </c>
       <c r="J3" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K3" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02248513102082483</v>
+        <v>0.02215663718433547</v>
       </c>
       <c r="M3" t="n">
-        <v>2.666103388790587</v>
+        <v>2.659641058105748</v>
       </c>
       <c r="N3" t="n">
-        <v>11.37071045736758</v>
+        <v>11.32763661468867</v>
       </c>
       <c r="O3" t="n">
-        <v>3.372048406735523</v>
+        <v>3.365655450976626</v>
       </c>
       <c r="P3" t="n">
-        <v>333.357725620718</v>
+        <v>333.3477188037116</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17275,28 +17337,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04215960555920822</v>
+        <v>-0.04160059352538478</v>
       </c>
       <c r="J4" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K4" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006568971824468695</v>
+        <v>0.006452655968385512</v>
       </c>
       <c r="M4" t="n">
-        <v>2.801431235132321</v>
+        <v>2.792670875239226</v>
       </c>
       <c r="N4" t="n">
-        <v>12.75139722160137</v>
+        <v>12.70005629287602</v>
       </c>
       <c r="O4" t="n">
-        <v>3.570909859069726</v>
+        <v>3.563713834313302</v>
       </c>
       <c r="P4" t="n">
-        <v>337.3371603383865</v>
+        <v>337.330717718742</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17334,7 +17396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E480"/>
+  <dimension ref="A1:E482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30297,6 +30359,60 @@
         </is>
       </c>
     </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>-45.37229562774976,170.86609863121737</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>-45.37263220933382,170.8653293115728</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>-45.37313914976412,170.8647702793077</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>-45.37229374364348,170.8660971338042</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>-45.37262946534175,170.86532620777578</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>-45.373138847664045,170.86476980627933</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0487/nzd0487.xlsx
+++ b/data/nzd0487/nzd0487.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E482"/>
+  <dimension ref="A1:E483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10556,6 +10556,27 @@
       <c r="E482" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>331.33</v>
+      </c>
+      <c r="C483" t="n">
+        <v>332.75</v>
+      </c>
+      <c r="D483" t="n">
+        <v>337.41</v>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B644"/>
+  <dimension ref="A1:B645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17013,6 +17034,16 @@
       </c>
       <c r="B644" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -17181,28 +17212,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07254444493684566</v>
+        <v>-0.06977055231400539</v>
       </c>
       <c r="J2" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K2" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00833212982100362</v>
+        <v>0.007724503354112455</v>
       </c>
       <c r="M2" t="n">
-        <v>4.464286177124981</v>
+        <v>4.465917223748403</v>
       </c>
       <c r="N2" t="n">
-        <v>29.85211286708101</v>
+        <v>29.87313298013291</v>
       </c>
       <c r="O2" t="n">
-        <v>5.463708709940621</v>
+        <v>5.46563198359832</v>
       </c>
       <c r="P2" t="n">
-        <v>326.9023492878503</v>
+        <v>326.8702966615057</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17259,28 +17290,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07338523057071536</v>
+        <v>-0.07279829183664703</v>
       </c>
       <c r="J3" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K3" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02215663718433547</v>
+        <v>0.02189882908112262</v>
       </c>
       <c r="M3" t="n">
-        <v>2.659641058105748</v>
+        <v>2.657222380276495</v>
       </c>
       <c r="N3" t="n">
-        <v>11.32763661468867</v>
+        <v>11.30784930639384</v>
       </c>
       <c r="O3" t="n">
-        <v>3.365655450976626</v>
+        <v>3.362714574030011</v>
       </c>
       <c r="P3" t="n">
-        <v>333.3477188037116</v>
+        <v>333.3409366637774</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17337,28 +17368,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04160059352538478</v>
+        <v>-0.04108519169023556</v>
       </c>
       <c r="J4" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K4" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006452655968385512</v>
+        <v>0.00632105635385638</v>
       </c>
       <c r="M4" t="n">
-        <v>2.792670875239226</v>
+        <v>2.789538094802123</v>
       </c>
       <c r="N4" t="n">
-        <v>12.70005629287602</v>
+        <v>12.6765714748795</v>
       </c>
       <c r="O4" t="n">
-        <v>3.563713834313302</v>
+        <v>3.560417317517639</v>
       </c>
       <c r="P4" t="n">
-        <v>337.330717718742</v>
+        <v>337.3247621953366</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17396,7 +17427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E482"/>
+  <dimension ref="A1:E483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30413,6 +30444,33 @@
         </is>
       </c>
     </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>-45.37230049502424,170.86610249953515</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>-45.37263333507415,170.8653305849255</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>-45.37314229160493,170.86477519880302</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0487/nzd0487.xlsx
+++ b/data/nzd0487/nzd0487.xlsx
@@ -10591,7 +10591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B645"/>
+  <dimension ref="A1:B647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17044,6 +17044,26 @@
       </c>
       <c r="B645" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0487/nzd0487.xlsx
+++ b/data/nzd0487/nzd0487.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E483"/>
+  <dimension ref="A1:E486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10577,6 +10577,69 @@
       <c r="E483" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>333.39</v>
+      </c>
+      <c r="C484" t="n">
+        <v>334.83</v>
+      </c>
+      <c r="D484" t="n">
+        <v>339.18</v>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="C485" t="n">
+        <v>332.74</v>
+      </c>
+      <c r="D485" t="n">
+        <v>336.27</v>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>331.04</v>
+      </c>
+      <c r="C486" t="n">
+        <v>332.95</v>
+      </c>
+      <c r="D486" t="n">
+        <v>336.85</v>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B647"/>
+  <dimension ref="A1:B650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17064,6 +17127,36 @@
       </c>
       <c r="B647" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -17232,28 +17325,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06977055231400539</v>
+        <v>-0.05986316937531703</v>
       </c>
       <c r="J2" t="n">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="K2" t="n">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007724503354112455</v>
+        <v>0.005707246179116887</v>
       </c>
       <c r="M2" t="n">
-        <v>4.465917223748403</v>
+        <v>4.476926635969468</v>
       </c>
       <c r="N2" t="n">
-        <v>29.87313298013291</v>
+        <v>30.04346629399274</v>
       </c>
       <c r="O2" t="n">
-        <v>5.46563198359832</v>
+        <v>5.481192050456976</v>
       </c>
       <c r="P2" t="n">
-        <v>326.8702966615057</v>
+        <v>326.7550130097042</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17310,28 +17403,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07279829183664703</v>
+        <v>-0.07005390485986426</v>
       </c>
       <c r="J3" t="n">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="K3" t="n">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02189882908112262</v>
+        <v>0.02052458526422096</v>
       </c>
       <c r="M3" t="n">
-        <v>2.657222380276495</v>
+        <v>2.654971525627246</v>
       </c>
       <c r="N3" t="n">
-        <v>11.30784930639384</v>
+        <v>11.27007492285901</v>
       </c>
       <c r="O3" t="n">
-        <v>3.362714574030011</v>
+        <v>3.357093225226105</v>
       </c>
       <c r="P3" t="n">
-        <v>333.3409366637774</v>
+        <v>333.3090079762394</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17388,28 +17481,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04108519169023556</v>
+        <v>-0.03952266812864043</v>
       </c>
       <c r="J4" t="n">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="K4" t="n">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00632105635385638</v>
+        <v>0.005922604295514611</v>
       </c>
       <c r="M4" t="n">
-        <v>2.789538094802123</v>
+        <v>2.780181229425058</v>
       </c>
       <c r="N4" t="n">
-        <v>12.6765714748795</v>
+        <v>12.61661788538276</v>
       </c>
       <c r="O4" t="n">
-        <v>3.560417317517639</v>
+        <v>3.551987877989276</v>
       </c>
       <c r="P4" t="n">
-        <v>337.3247621953366</v>
+        <v>337.3065889654575</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17447,7 +17540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E483"/>
+  <dimension ref="A1:E486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30491,6 +30584,87 @@
         </is>
       </c>
     </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>-45.37231666693531,170.86611535233757</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>-45.372647969697056,170.8653471385152</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>-45.37315298594616,170.8647919440124</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>-45.37231627441323,170.86611504037626</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>-45.372633264715375,170.86533050534095</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>-45.37313540372289,170.86476441375626</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>-45.37229821839586,170.8661006901606</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>-45.37263474224953,170.86533217661645</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>-45.37313890808406,170.864769900885</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0487/nzd0487.xlsx
+++ b/data/nzd0487/nzd0487.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E486"/>
+  <dimension ref="A1:E491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10638,6 +10638,111 @@
         <v>336.85</v>
       </c>
       <c r="E486" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>329.78</v>
+      </c>
+      <c r="C487" t="n">
+        <v>332.74</v>
+      </c>
+      <c r="D487" t="n">
+        <v>336.23</v>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:04+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>329.95</v>
+      </c>
+      <c r="C488" t="n">
+        <v>332.74</v>
+      </c>
+      <c r="D488" t="n">
+        <v>331.28</v>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>329.95</v>
+      </c>
+      <c r="C489" t="n">
+        <v>332.74</v>
+      </c>
+      <c r="D489" t="n">
+        <v>328.24</v>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>326.95</v>
+      </c>
+      <c r="C490" t="n">
+        <v>331.55</v>
+      </c>
+      <c r="D490" t="n">
+        <v>327.43</v>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>326.08</v>
+      </c>
+      <c r="C491" t="n">
+        <v>330.26</v>
+      </c>
+      <c r="D491" t="n">
+        <v>326.81</v>
+      </c>
+      <c r="E491" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10654,7 +10759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B650"/>
+  <dimension ref="A1:B655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17157,6 +17262,56 @@
       </c>
       <c r="B650" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -17325,28 +17480,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05986316937531703</v>
+        <v>-0.0526916798288006</v>
       </c>
       <c r="J2" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="K2" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005707246179116887</v>
+        <v>0.004504120276330958</v>
       </c>
       <c r="M2" t="n">
-        <v>4.476926635969468</v>
+        <v>4.459300783572012</v>
       </c>
       <c r="N2" t="n">
-        <v>30.04346629399274</v>
+        <v>29.87842484889806</v>
       </c>
       <c r="O2" t="n">
-        <v>5.481192050456976</v>
+        <v>5.466116066175147</v>
       </c>
       <c r="P2" t="n">
-        <v>326.7550130097042</v>
+        <v>326.6713928085248</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17403,28 +17558,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07005390485986426</v>
+        <v>-0.06886144805731334</v>
       </c>
       <c r="J3" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="K3" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02052458526422096</v>
+        <v>0.02025486640884933</v>
       </c>
       <c r="M3" t="n">
-        <v>2.654971525627246</v>
+        <v>2.638881970396998</v>
       </c>
       <c r="N3" t="n">
-        <v>11.27007492285901</v>
+        <v>11.16812217113509</v>
       </c>
       <c r="O3" t="n">
-        <v>3.357093225226105</v>
+        <v>3.341874050758809</v>
       </c>
       <c r="P3" t="n">
-        <v>333.3090079762394</v>
+        <v>333.2951178164244</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17481,28 +17636,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03952266812864043</v>
+        <v>-0.05283486319062706</v>
       </c>
       <c r="J4" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="K4" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005922604295514611</v>
+        <v>0.01034887357332359</v>
       </c>
       <c r="M4" t="n">
-        <v>2.780181229425058</v>
+        <v>2.812171202934968</v>
       </c>
       <c r="N4" t="n">
-        <v>12.61661788538276</v>
+        <v>12.9979343316779</v>
       </c>
       <c r="O4" t="n">
-        <v>3.551987877989276</v>
+        <v>3.605264807427868</v>
       </c>
       <c r="P4" t="n">
-        <v>337.3065889654575</v>
+        <v>337.4619608672782</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17540,7 +17695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E486"/>
+  <dimension ref="A1:E491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30665,6 +30820,141 @@
         </is>
       </c>
     </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>-45.372288326837825,170.86609282874193</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>-45.372633264715375,170.86533050534095</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>-45.3731351620428,170.86476403533365</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:04+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>-45.372289661413134,170.86609388940937</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>-45.372633264715375,170.86533050534095</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>-45.37310525412244,170.86471720555622</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>-45.372289661413134,170.86609388940937</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>-45.372633264715375,170.86533050534095</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>-45.37308688642078,170.86468844547502</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>-45.37226611008256,170.86607517175585</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-45.37262489202142,170.86532103478146</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-45.373081992393836,170.86468078243024</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>-45.37225928019617,170.8660697436392</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-45.37261581573892,170.86531076837977</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-45.373078246348186,170.86467491689066</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0487/nzd0487.xlsx
+++ b/data/nzd0487/nzd0487.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E491"/>
+  <dimension ref="A1:E496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10743,6 +10743,111 @@
         <v>326.81</v>
       </c>
       <c r="E491" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>325.87</v>
+      </c>
+      <c r="C492" t="n">
+        <v>329.46</v>
+      </c>
+      <c r="D492" t="n">
+        <v>326.86</v>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:53+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>323.92</v>
+      </c>
+      <c r="C493" t="n">
+        <v>328.95</v>
+      </c>
+      <c r="D493" t="n">
+        <v>326.03</v>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>324.16</v>
+      </c>
+      <c r="C494" t="n">
+        <v>328.94</v>
+      </c>
+      <c r="D494" t="n">
+        <v>326.44</v>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="C495" t="n">
+        <v>329.71</v>
+      </c>
+      <c r="D495" t="n">
+        <v>326.86</v>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>322.22</v>
+      </c>
+      <c r="C496" t="n">
+        <v>330</v>
+      </c>
+      <c r="D496" t="n">
+        <v>327.97</v>
+      </c>
+      <c r="E496" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10759,7 +10864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B655"/>
+  <dimension ref="A1:B661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17312,6 +17417,66 @@
       </c>
       <c r="B655" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -17480,28 +17645,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0526916798288006</v>
+        <v>-0.05573518034127384</v>
       </c>
       <c r="J2" t="n">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="K2" t="n">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004504120276330958</v>
+        <v>0.005139152455656881</v>
       </c>
       <c r="M2" t="n">
-        <v>4.459300783572012</v>
+        <v>4.433846661780526</v>
       </c>
       <c r="N2" t="n">
-        <v>29.87842484889806</v>
+        <v>29.61330422813614</v>
       </c>
       <c r="O2" t="n">
-        <v>5.466116066175147</v>
+        <v>5.441810749018762</v>
       </c>
       <c r="P2" t="n">
-        <v>326.6713928085248</v>
+        <v>326.707051271252</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17558,28 +17723,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06886144805731334</v>
+        <v>-0.07310796263882512</v>
       </c>
       <c r="J3" t="n">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="K3" t="n">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02025486640884933</v>
+        <v>0.02316658174889019</v>
       </c>
       <c r="M3" t="n">
-        <v>2.638881970396998</v>
+        <v>2.630782700376437</v>
       </c>
       <c r="N3" t="n">
-        <v>11.16812217113509</v>
+        <v>11.09801025866552</v>
       </c>
       <c r="O3" t="n">
-        <v>3.341874050758809</v>
+        <v>3.331367625865618</v>
       </c>
       <c r="P3" t="n">
-        <v>333.2951178164244</v>
+        <v>333.3448252722926</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17636,28 +17801,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05283486319062706</v>
+        <v>-0.07197364412209402</v>
       </c>
       <c r="J4" t="n">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="K4" t="n">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01034887357332359</v>
+        <v>0.0182766673496001</v>
       </c>
       <c r="M4" t="n">
-        <v>2.812171202934968</v>
+        <v>2.874480772985943</v>
       </c>
       <c r="N4" t="n">
-        <v>12.9979343316779</v>
+        <v>13.70238918856732</v>
       </c>
       <c r="O4" t="n">
-        <v>3.605264807427868</v>
+        <v>3.701673836059482</v>
       </c>
       <c r="P4" t="n">
-        <v>337.4619608672782</v>
+        <v>337.6860048260156</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17695,7 +17860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E491"/>
+  <dimension ref="A1:E496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30955,6 +31120,141 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>-45.372257631602864,170.8660684334043</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>-45.372610187036145,170.86530440162068</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>-45.37307854844865,170.86467538991803</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:53+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>-45.37224232323578,170.8660562669413</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>-45.372606598737946,170.8653003428124</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-45.373073533580666,170.8646675376646</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>-45.372244207342575,170.8660577643518</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>-45.37260652837915,170.8653002632279</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>-45.37307601080467,170.8646714164884</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>-45.372233923259486,170.86604959098744</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>-45.3726119460058,170.86530639123276</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>-45.37307854844865,170.86467538991803</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>-45.372228977478876,170.86604566028655</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>-45.37261398641055,170.86530869918292</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>-45.37308525507852,170.8646858911266</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0487/nzd0487.xlsx
+++ b/data/nzd0487/nzd0487.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E496"/>
+  <dimension ref="A1:E498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10848,6 +10848,48 @@
         <v>327.97</v>
       </c>
       <c r="E496" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>321.84</v>
+      </c>
+      <c r="C497" t="n">
+        <v>328.75</v>
+      </c>
+      <c r="D497" t="n">
+        <v>326.72</v>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>320.86</v>
+      </c>
+      <c r="C498" t="n">
+        <v>328.92</v>
+      </c>
+      <c r="D498" t="n">
+        <v>327.31</v>
+      </c>
+      <c r="E498" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10864,7 +10906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B661"/>
+  <dimension ref="A1:B663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17477,6 +17519,26 @@
       </c>
       <c r="B661" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -17645,28 +17707,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05573518034127384</v>
+        <v>-0.05893513480898363</v>
       </c>
       <c r="J2" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K2" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005139152455656881</v>
+        <v>0.005779787422544702</v>
       </c>
       <c r="M2" t="n">
-        <v>4.433846661780526</v>
+        <v>4.433872653200424</v>
       </c>
       <c r="N2" t="n">
-        <v>29.61330422813614</v>
+        <v>29.55435217174977</v>
       </c>
       <c r="O2" t="n">
-        <v>5.441810749018762</v>
+        <v>5.436391466013992</v>
       </c>
       <c r="P2" t="n">
-        <v>326.707051271252</v>
+        <v>326.7446718768045</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17723,28 +17785,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07310796263882512</v>
+        <v>-0.07522243221598109</v>
       </c>
       <c r="J3" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K3" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02316658174889019</v>
+        <v>0.02464057527438757</v>
       </c>
       <c r="M3" t="n">
-        <v>2.630782700376437</v>
+        <v>2.629310874338245</v>
       </c>
       <c r="N3" t="n">
-        <v>11.09801025866552</v>
+        <v>11.07925974496869</v>
       </c>
       <c r="O3" t="n">
-        <v>3.331367625865618</v>
+        <v>3.328552199525897</v>
       </c>
       <c r="P3" t="n">
-        <v>333.3448252722926</v>
+        <v>333.3696824703266</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17801,28 +17863,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07197364412209402</v>
+        <v>-0.07921508904918521</v>
       </c>
       <c r="J4" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K4" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0182766673496001</v>
+        <v>0.02176469427849514</v>
       </c>
       <c r="M4" t="n">
-        <v>2.874480772985943</v>
+        <v>2.897814944631342</v>
       </c>
       <c r="N4" t="n">
-        <v>13.70238918856732</v>
+        <v>13.95110959400751</v>
       </c>
       <c r="O4" t="n">
-        <v>3.701673836059482</v>
+        <v>3.735118417668644</v>
       </c>
       <c r="P4" t="n">
-        <v>337.6860048260156</v>
+        <v>337.7711335571437</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17860,7 +17922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E496"/>
+  <dimension ref="A1:E498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31255,6 +31317,60 @@
         </is>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>-45.37222599430955,170.8660432893879</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-45.372605191562144,170.86529875112302</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-45.37307770256734,170.86467406544145</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-45.37221830087267,170.86603717496627</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-45.37260638766157,170.865300104059</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-45.37308126735276,170.86467964716448</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
